--- a/data/trans_orig/IP16B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B01-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58556</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79732</t>
+          <t>79663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264198</t>
+          <t>264520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>44333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42670</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21839</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>35071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>43064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46148</t>
+          <t>46889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55442</t>
+          <t>55670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164724</t>
+          <t>165258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179957</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22553</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>41633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48743</t>
+          <t>48756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>29916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31868</t>
+          <t>32002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67099</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>113767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127644</t>
+          <t>127868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
